--- a/templates/000_pm_suite/02_프로젝트 개발/07_전개/01_오픈 및 안정화/프로젝트명_이행계획서_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/07_전개/01_오픈 및 안정화/프로젝트명_이행계획서_V1.0_20230530.xlsx
@@ -3057,12 +3057,12 @@
     <row r="17" ht="21.75" customHeight="1" s="112">
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI</t>
+          <t>한빛글로벌 SyncFlow AI</t>
         </is>
       </c>
       <c r="C17" s="93" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D17" s="113" t="n"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
@@ -3423,7 +3423,7 @@
     <row r="1">
       <c r="A1" s="124" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 이행 체크리스트 (Cut-over Checklist)</t>
+          <t>SyncFlow AI 시스템 이행 체크리스트 (Cut-over Checklist)</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E9" s="129" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 의뢰 수신/판정 결과 회신 API 및 SSO 연동 통합 검증</t>
+          <t>전자구매포털(SRM-Portal) 의뢰 수신/판정 결과 회신 API 및 SSO 연동 통합 검증</t>
         </is>
       </c>
       <c r="F9" s="129" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="I9" s="130" t="inlineStr">
         <is>
-          <t>IF-CLM-001, IF-CLM-002 정상 응답</t>
+          <t>IF-REV-001, IF-REV-002 정상 응답</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E10" s="126" t="inlineStr">
         <is>
-          <t>프로덕트랩(ProductLab) 처방/전성분 배합한도 및 인체적용시험 실증보고서 연동 확인</t>
+          <t>피엘엠넥서스(PLM-Nexus) 설계사양/자재BOM 유해물질한도 및 공인신뢰성시험 시험검증보고서 연동 확인</t>
         </is>
       </c>
       <c r="F10" s="126" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I10" s="127" t="inlineStr">
         <is>
-          <t>IF-CLM-003, IF-CLM-004 정합성 확인</t>
+          <t>IF-REV-003, IF-REV-004 정합성 확인</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="E12" s="126" t="inlineStr">
         <is>
-          <t>동영상(MP4) 사용자 지정 다중 장면 스냅샷 캡처 및 S3 일괄 AI 검토 기능 확인</t>
+          <t>설계도면(CAD/PDF) 사용자 지정 다중 장면 스냅샷 스냅샷 및 S3 일괄 AI 검토 기능 확인</t>
         </is>
       </c>
       <c r="F12" s="126" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="E13" s="129" t="inlineStr">
         <is>
-          <t>RA 골든셋(판례/금칙어) 정합성 테스트 및 취약점 진단 조치 완료 확인</t>
+          <t>QA 골든셋(판례/금칙어) 정합성 테스트 및 취약점 진단 조치 완료 확인</t>
         </is>
       </c>
       <c r="F13" s="129" t="inlineStr">
         <is>
-          <t>QA/RA Lab</t>
+          <t>QA/품질법무검증팀</t>
         </is>
       </c>
       <c r="G13" s="129" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="E14" s="126" t="inlineStr">
         <is>
-          <t>RA 현업 담당자 및 IT 운영자 매뉴얼 배포, 사용자 교육 완료 확인</t>
+          <t>QA 현업 담당자 및 IT 운영자 매뉴얼 배포, 사용자 교육 완료 확인</t>
         </is>
       </c>
       <c r="F14" s="126" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="C15" s="130" t="inlineStr">
         <is>
-          <t>운영 환경 실 시안 등록 ➔ OCR ➔ 3단계 AI 판정 ➔ RA 승인 ➔ PDF 출력 전수 점검</t>
+          <t>운영 환경 실 계약·도서 등록 ➔ OCR ➔ 3단계 AI 판정 ➔ QA 승인 ➔ PDF 출력 전수 점검</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C16" s="127" t="inlineStr">
         <is>
-          <t>한빛글로벌 전사 마케팅 부서 대상 SyncGuard AI 정식 서비스 오픈 안내</t>
+          <t>한빛글로벌 전사 구매조달 부서 대상 SyncFlow AI 정식 서비스 오픈 안내</t>
         </is>
       </c>
       <c r="D16" s="126" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C17" s="130" t="inlineStr">
         <is>
-          <t>오픈 초기 마케터 집중 의뢰 모니터링 및 비정형 시안 처리 워커 집중 관제</t>
+          <t>오픈 초기 구매담당자 집중 의뢰 모니터링 및 비정형 계약·도서 처리 워커 집중 관제</t>
         </is>
       </c>
       <c r="D17" s="129" t="inlineStr">
